--- a/resource/groundTruths/requirement/CF_M01_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M01_ground_truth_requirement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0F044A-9885-E745-A440-A3E38EB567C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE71654D-35D9-464D-93E7-1E7BAC13E31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
   <si>
     <t>Document ID</t>
   </si>
@@ -150,9 +150,6 @@
     <t>The actions that the user will be able to see will depend on the permissions it has</t>
   </si>
   <si>
-    <t>CF_M01_R015</t>
-  </si>
-  <si>
     <t>CF_M01_R17</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
   </si>
   <si>
     <t>The system responds to any user action in less than 5 seconds.</t>
-  </si>
-  <si>
-    <t>CF_M01_R018</t>
   </si>
   <si>
     <t>CF_M01_R20</t>
@@ -208,9 +202,6 @@
     <t>Unauthorized users cannot access data they do not own.</t>
   </si>
   <si>
-    <t>CF_M01_R023</t>
-  </si>
-  <si>
     <t>CF_M01_R25</t>
   </si>
   <si>
@@ -224,9 +215,6 @@
     <t>Users can only view their confidential data user and no one else.</t>
   </si>
   <si>
-    <t>CF_M01_R025</t>
-  </si>
-  <si>
     <t>CF_M01_R28</t>
   </si>
   <si>
@@ -273,9 +261,6 @@
   </si>
   <si>
     <t>The system scales automatically as they go increasing the data.</t>
-  </si>
-  <si>
-    <t>CF_M01_C07</t>
   </si>
   <si>
     <t>n the case of this project, within the software engineering it will focus on web development technologies and more specifically on the backend. As a framework, NestJS [2] will be used, with the Typescript language [3], and for the infrastructure, AWS cloud services [4] will be used. These technologies are the same as those currently used in the Waapiti company.</t>
@@ -695,7 +680,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -994,7 +979,7 @@
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G17">
         <v>37</v>
@@ -1005,16 +990,16 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
         <v>43</v>
       </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
       <c r="D18" t="s">
         <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G18">
         <v>37</v>
@@ -1025,16 +1010,16 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
         <v>45</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="G19">
         <v>37</v>
@@ -1045,16 +1030,16 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
       <c r="D20" t="s">
         <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G20">
         <v>37</v>
@@ -1065,16 +1050,16 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G21">
         <v>38</v>
@@ -1085,16 +1070,16 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G22">
         <v>38</v>
@@ -1105,16 +1090,16 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G23">
         <v>38</v>
@@ -1125,16 +1110,16 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G24">
         <v>38</v>
@@ -1145,16 +1130,16 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G25">
         <v>38</v>
@@ -1165,16 +1150,16 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>38</v>
@@ -1185,16 +1170,16 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G27">
         <v>39</v>
@@ -1205,16 +1190,16 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G28">
         <v>39</v>
@@ -1225,16 +1210,16 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G29">
         <v>39</v>
@@ -1245,16 +1230,16 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G30">
         <v>39</v>
@@ -1265,13 +1250,13 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -1292,10 +1277,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1303,10 +1288,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1314,10 +1299,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1325,10 +1310,10 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1336,10 +1321,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1347,10 +1332,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1358,50 +1343,50 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
